--- a/data/naverland.xlsx
+++ b/data/naverland.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="매물목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="매물목록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -432,67 +444,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>수집일시</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>단지코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>단지명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>매물번호</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>공급평형</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>전용평형</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>공급면적(m2)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>전용면적(m2)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>매매가</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>매매가(원)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>층정보</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>등록/확인일</t>
         </is>
@@ -501,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -558,7 +570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,7 +627,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -672,7 +684,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -687,7 +699,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2631663732</t>
+          <t>2634503184</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -704,32 +716,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30억</t>
+          <t>29억 7,000</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3000000000</v>
+        <v>2970000000</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -744,7 +756,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2632586407</t>
+          <t>2631663732</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -761,15 +773,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29억 9,500</t>
+          <t>30억</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2995000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>중/12</t>
+          <t>4/12</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -779,14 +791,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -843,7 +855,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +912,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -957,7 +969,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,7 +1026,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1029,7 +1041,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2633753342</t>
+          <t>2634670888</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1046,32 +1058,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30억 8,000</t>
+          <t>30억</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3080000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>5/12</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1086,7 +1098,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2633492822</t>
+          <t>2633753342</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1103,32 +1115,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30억</t>
+          <t>30억 8,000</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3000000000</v>
+        <v>3080000000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1185,7 +1197,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1242,7 +1254,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1299,7 +1311,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1356,7 +1368,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1371,7 +1383,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2631661706</t>
+          <t>2630690375</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1396,7 +1408,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>3/12</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1406,14 +1418,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1428,49 +1440,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2631661405</t>
+          <t>2634539327</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>31.6</v>
+        <v>42.8</v>
       </c>
       <c r="F18" t="n">
-        <v>29.2</v>
+        <v>39.7</v>
       </c>
       <c r="G18" t="n">
-        <v>104.6</v>
+        <v>141.57</v>
       </c>
       <c r="H18" t="n">
-        <v>96.65000000000001</v>
+        <v>131.08</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>34억</t>
+          <t>41억</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3400000000</v>
+        <v>4100000000</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1485,49 +1497,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2630690375</t>
+          <t>2634099789</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>31.6</v>
+        <v>42.8</v>
       </c>
       <c r="F19" t="n">
-        <v>29.2</v>
+        <v>39.7</v>
       </c>
       <c r="G19" t="n">
-        <v>104.6</v>
+        <v>141.57</v>
       </c>
       <c r="H19" t="n">
-        <v>96.65000000000001</v>
+        <v>131.08</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3500000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1542,7 +1554,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2634450467</t>
+          <t>2633965856</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1559,15 +1571,15 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>41억</t>
+          <t>39억</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4100000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1577,14 +1589,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1599,7 +1611,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2634099789</t>
+          <t>2633977832</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1634,14 +1646,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1656,7 +1668,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2633965856</t>
+          <t>2633130337</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1673,15 +1685,15 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>39억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>6/12</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1691,14 +1703,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1713,7 +1725,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2633977832</t>
+          <t>2633978876</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1738,7 +1750,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>중/12</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1755,7 +1767,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1770,7 +1782,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2633130337</t>
+          <t>2632656877</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1795,7 +1807,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1805,14 +1817,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1827,7 +1839,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2633978876</t>
+          <t>2632708399</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1844,15 +1856,15 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>39억</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>중/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1862,14 +1874,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1884,7 +1896,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2632656877</t>
+          <t>2631241203</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1901,11 +1913,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>42억</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1919,14 +1931,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1941,49 +1953,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2632708399</t>
+          <t>2632792587</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>42.8</v>
+        <v>43.8</v>
       </c>
       <c r="F27" t="n">
-        <v>39.7</v>
+        <v>41.2</v>
       </c>
       <c r="G27" t="n">
-        <v>141.57</v>
+        <v>144.85</v>
       </c>
       <c r="H27" t="n">
-        <v>131.08</v>
+        <v>136.34</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>39억</t>
+          <t>41억 5,000</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3900000000</v>
+        <v>4150000000</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1998,32 +2010,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2631241203</t>
+          <t>2634165837</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>42.8</v>
+        <v>43.8</v>
       </c>
       <c r="F28" t="n">
-        <v>39.7</v>
+        <v>41.2</v>
       </c>
       <c r="G28" t="n">
-        <v>141.57</v>
+        <v>144.85</v>
       </c>
       <c r="H28" t="n">
-        <v>131.08</v>
+        <v>136.34</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>42억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>4200000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>5/15</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2033,14 +2045,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2055,7 +2067,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2632792587</t>
+          <t>2631664005</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2072,32 +2084,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>41억 5,000</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4150000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>중/15</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2112,32 +2124,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2634165837</t>
+          <t>2634170812</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>43.8</v>
+        <v>52.5</v>
       </c>
       <c r="F30" t="n">
-        <v>41.2</v>
+        <v>48.6</v>
       </c>
       <c r="G30" t="n">
-        <v>144.85</v>
+        <v>173.63</v>
       </c>
       <c r="H30" t="n">
-        <v>136.34</v>
+        <v>160.74</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>44억</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4000000000</v>
+        <v>4400000000</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2154,7 +2166,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2169,32 +2181,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2631664005</t>
+          <t>2633967484</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>43.8</v>
+        <v>52.5</v>
       </c>
       <c r="F31" t="n">
-        <v>41.2</v>
+        <v>48.6</v>
       </c>
       <c r="G31" t="n">
-        <v>144.85</v>
+        <v>173.63</v>
       </c>
       <c r="H31" t="n">
-        <v>136.34</v>
+        <v>160.74</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>44억</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4000000000</v>
+        <v>4400000000</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>중/15</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2204,14 +2216,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2226,7 +2238,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2634170812</t>
+          <t>2633977168</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2243,15 +2255,15 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>44억</t>
+          <t>46억</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4400000000</v>
+        <v>4600000000</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2261,14 +2273,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2283,7 +2295,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2633977168</t>
+          <t>2634099689</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2308,7 +2320,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2318,14 +2330,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2340,7 +2352,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2633967484</t>
+          <t>2632739974</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2357,15 +2369,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>44억</t>
+          <t>43억 9,000</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4400000000</v>
+        <v>4390000000</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2375,14 +2387,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2397,7 +2409,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2634099689</t>
+          <t>2633201694</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2414,15 +2426,15 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>46억</t>
+          <t>45억</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4600000000</v>
+        <v>4500000000</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2432,7 +2444,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -2454,32 +2466,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2632739974</t>
+          <t>2634143650</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>52.5</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
-        <v>48.6</v>
+        <v>24.3</v>
       </c>
       <c r="G36" t="n">
-        <v>173.63</v>
+        <v>86.09</v>
       </c>
       <c r="H36" t="n">
-        <v>160.74</v>
+        <v>80.39</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>43억 9,000</t>
+          <t>30억 5,000</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4390000000</v>
+        <v>3050000000</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>중/12</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2489,7 +2501,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -2511,40 +2523,1978 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>2633978112</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>29억 7,000</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2970000000</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2634142469</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H38" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30억</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2631663732</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H39" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30억</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2632586407</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H40" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>29억 9,500</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>2995000000</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2630437810</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H41" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>31억</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2630439804</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H42" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>31억</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2634171154</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G43" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30억 5,000</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>3050000000</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2632660872</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="H44" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>29억 7,000</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2970000000</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2633753342</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30억 8,000</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>3080000000</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2633492822</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30억</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2634439099</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>35억</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2634344796</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>34억</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2633805075</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>34억</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2631662478</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>34억 5,000</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>3450000000</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2631661706</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>35억</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2631661405</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>34억</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2630690375</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>35억</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2634450467</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G54" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H54" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>41억</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>4100000000</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2634099789</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G55" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H55" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2633965856</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G56" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H56" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>39억</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2633977832</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G57" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H57" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2633130337</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G58" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H58" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2633978876</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H59" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2632656877</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F60" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H60" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2632708399</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F61" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G61" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H61" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>39억</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2631241203</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F62" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G62" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H62" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>42억</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2632792587</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="H63" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>41억 5,000</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>4150000000</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2634165837</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F64" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="H64" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2631664005</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F65" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="H65" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>중/15</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2634170812</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H66" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>44억</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>4400000000</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2633977168</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H67" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>46억</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>4600000000</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2633967484</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H68" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>44억</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>4400000000</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2634099689</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G69" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H69" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>46억</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>4600000000</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2632739974</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H70" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>43억 9,000</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>4390000000</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>2633201694</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E71" t="n">
         <v>52.5</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F71" t="n">
         <v>48.6</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G71" t="n">
         <v>173.63</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H71" t="n">
         <v>160.74</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>45억</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J71" t="n">
         <v>4500000000</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>2/12</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>

--- a/data/naverland.xlsx
+++ b/data/naverland.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2633978112</t>
+          <t>2634752989</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -620,14 +620,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2634142469</t>
+          <t>2634945231</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -659,11 +659,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30억</t>
+          <t>29억 7,000</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3000000000</v>
+        <v>2970000000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2634503184</t>
+          <t>2634142469</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -716,11 +716,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>29억 7,000</t>
+          <t>30억</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2970000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -734,14 +734,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2634171154</t>
+          <t>2634753533</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -962,14 +962,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2634670888</t>
+          <t>2634903611</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1076,14 +1076,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1140,7 +1140,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2634439099</t>
+          <t>2634945208</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1254,7 +1254,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2631662478</t>
+          <t>2630690375</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1343,32 +1343,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34억 5,000</t>
+          <t>35억</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3450000000</v>
+        <v>3500000000</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>3/12</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1383,28 +1383,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2630690375</t>
+          <t>2634895760</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>31.6</v>
+        <v>42.8</v>
       </c>
       <c r="F17" t="n">
-        <v>29.2</v>
+        <v>39.7</v>
       </c>
       <c r="G17" t="n">
-        <v>104.6</v>
+        <v>141.57</v>
       </c>
       <c r="H17" t="n">
-        <v>96.65000000000001</v>
+        <v>131.08</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3500000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1413,19 +1413,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2634539327</t>
+          <t>2634915357</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1475,14 +1475,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2633965856</t>
+          <t>2633977832</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1571,15 +1571,15 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>39억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2633977832</t>
+          <t>2633965856</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1628,15 +1628,15 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>39억</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2633130337</t>
+          <t>2634753986</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>중/12</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1703,14 +1703,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2633978876</t>
+          <t>2634821833</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1760,14 +1760,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2632656877</t>
+          <t>2633130337</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1799,15 +1799,15 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>41억</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>4000000000</v>
+        <v>4100000000</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>6/12</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2632708399</t>
+          <t>2632656877</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1856,15 +1856,15 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>39억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2631241203</t>
+          <t>2632708399</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>42억</t>
+          <t>39억</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4200000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1953,49 +1953,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2632792587</t>
+          <t>2631241203</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>43.8</v>
+        <v>42.8</v>
       </c>
       <c r="F27" t="n">
-        <v>41.2</v>
+        <v>39.7</v>
       </c>
       <c r="G27" t="n">
-        <v>144.85</v>
+        <v>141.57</v>
       </c>
       <c r="H27" t="n">
-        <v>136.34</v>
+        <v>131.08</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>41억 5,000</t>
+          <t>42억</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>4150000000</v>
+        <v>4200000000</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2634165837</t>
+          <t>2632792587</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2027,32 +2027,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>41억 5,000</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>4000000000</v>
+        <v>4150000000</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2631664005</t>
+          <t>2634165837</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>중/15</t>
+          <t>5/15</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2634170812</t>
+          <t>2631664005</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>52.5</v>
+        <v>43.8</v>
       </c>
       <c r="F30" t="n">
-        <v>48.6</v>
+        <v>41.2</v>
       </c>
       <c r="G30" t="n">
-        <v>173.63</v>
+        <v>144.85</v>
       </c>
       <c r="H30" t="n">
-        <v>160.74</v>
+        <v>136.34</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>44억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4400000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>중/15</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2159,14 +2159,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2633967484</t>
+          <t>2634170812</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2216,14 +2216,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2633977168</t>
+          <t>2633967484</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2255,15 +2255,15 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>46억</t>
+          <t>44억</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4600000000</v>
+        <v>4400000000</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2280,7 +2280,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2634099689</t>
+          <t>2633977168</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2330,14 +2330,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2632739974</t>
+          <t>2634783712</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2369,15 +2369,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>43억 9,000</t>
+          <t>46억</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4390000000</v>
+        <v>4600000000</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-28T12:09:27</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2633201694</t>
+          <t>2632739974</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2426,15 +2426,15 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45억</t>
+          <t>43억 9,000</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4500000000</v>
+        <v>4390000000</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-30T06:45:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2466,32 +2466,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2634143650</t>
+          <t>2633201694</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>52.5</v>
       </c>
       <c r="F36" t="n">
-        <v>24.3</v>
+        <v>48.6</v>
       </c>
       <c r="G36" t="n">
-        <v>86.09</v>
+        <v>173.63</v>
       </c>
       <c r="H36" t="n">
-        <v>80.39</v>
+        <v>160.74</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30억 5,000</t>
+          <t>45억</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>3050000000</v>
+        <v>4500000000</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>중/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2523,32 +2523,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2633978112</t>
+          <t>2634143650</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="F37" t="n">
         <v>24.3</v>
       </c>
       <c r="G37" t="n">
-        <v>86.13</v>
+        <v>86.09</v>
       </c>
       <c r="H37" t="n">
-        <v>80.34999999999999</v>
+        <v>80.39</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29억 7,000</t>
+          <t>30억 5,000</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2970000000</v>
+        <v>3050000000</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>중/12</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2558,14 +2558,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2634142469</t>
+          <t>2633978112</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2597,15 +2597,15 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30억</t>
+          <t>29억 7,000</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3000000000</v>
+        <v>2970000000</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2615,14 +2615,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2631663732</t>
+          <t>2634142469</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2662,24 +2662,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2632586407</t>
+          <t>2634503184</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2711,32 +2711,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>29억 9,500</t>
+          <t>29억 7,000</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2995000000</v>
+        <v>2970000000</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>중/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2630437810</t>
+          <t>2631663732</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>31억</t>
+          <t>30억</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>3100000000</v>
+        <v>3000000000</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>중/12</t>
+          <t>4/12</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2630439804</t>
+          <t>2630437810</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2850,7 +2850,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2865,49 +2865,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2634171154</t>
+          <t>2630439804</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="F43" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="G43" t="n">
-        <v>86.45999999999999</v>
+        <v>86.13</v>
       </c>
       <c r="H43" t="n">
-        <v>80.76000000000001</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30억 5,000</t>
+          <t>31억</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3050000000</v>
+        <v>3100000000</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>중/12</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2632660872</t>
+          <t>2634171154</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2932,22 +2932,22 @@
         <v>24.4</v>
       </c>
       <c r="G44" t="n">
-        <v>86.56</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>80.78</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>29억 7,000</t>
+          <t>30억 5,000</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>2970000000</v>
+        <v>3050000000</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2957,14 +2957,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2979,49 +2979,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2633753342</t>
+          <t>2632660872</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="F45" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="G45" t="n">
-        <v>87.93000000000001</v>
+        <v>86.56</v>
       </c>
       <c r="H45" t="n">
-        <v>82.06</v>
+        <v>80.78</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30억 8,000</t>
+          <t>29억 7,000</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>3080000000</v>
+        <v>2970000000</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2633492822</t>
+          <t>2634670888</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3093,32 +3093,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2634439099</t>
+          <t>2633753342</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31.6</v>
+        <v>26.6</v>
       </c>
       <c r="F47" t="n">
-        <v>29.2</v>
+        <v>24.8</v>
       </c>
       <c r="G47" t="n">
-        <v>104.6</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>96.65000000000001</v>
+        <v>82.06</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>35억</t>
+          <t>30억 8,000</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>3500000000</v>
+        <v>3080000000</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3128,14 +3128,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2634344796</t>
+          <t>2634439099</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3167,20 +3167,20 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>34억</t>
+          <t>35억</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>3400000000</v>
+        <v>3500000000</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2633805075</t>
+          <t>2634344796</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3242,14 +3242,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2631662478</t>
+          <t>2633805075</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3281,32 +3281,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>34억 5,000</t>
+          <t>34억</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>3450000000</v>
+        <v>3400000000</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2631661706</t>
+          <t>2631662478</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3338,20 +3338,20 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>35억</t>
+          <t>34억 5,000</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>3500000000</v>
+        <v>3450000000</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3363,7 +3363,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2631661405</t>
+          <t>2630690375</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3395,15 +3395,15 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>34억</t>
+          <t>35억</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>3400000000</v>
+        <v>3500000000</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>3/12</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3413,14 +3413,14 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3435,49 +3435,49 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2630690375</t>
+          <t>2634539327</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>31.6</v>
+        <v>42.8</v>
       </c>
       <c r="F53" t="n">
-        <v>29.2</v>
+        <v>39.7</v>
       </c>
       <c r="G53" t="n">
-        <v>104.6</v>
+        <v>141.57</v>
       </c>
       <c r="H53" t="n">
-        <v>96.65000000000001</v>
+        <v>131.08</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>35억</t>
+          <t>41억</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>3500000000</v>
+        <v>4100000000</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2634450467</t>
+          <t>2634099789</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3509,15 +3509,15 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>41억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>4100000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3527,14 +3527,14 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2634099789</t>
+          <t>2633965856</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -3566,15 +3566,15 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>39억</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>1/12</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2633965856</t>
+          <t>2633977832</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -3623,15 +3623,15 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>39억</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>3900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3648,7 +3648,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2633977832</t>
+          <t>2633130337</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12/12</t>
+          <t>6/12</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3698,14 +3698,14 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2633130337</t>
+          <t>2633978876</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>중/12</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3755,14 +3755,14 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2633978876</t>
+          <t>2632656877</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>중/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3812,14 +3812,14 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2632656877</t>
+          <t>2632708399</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3851,15 +3851,15 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>39억</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>4000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3876,7 +3876,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2632708399</t>
+          <t>2631241203</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3908,15 +3908,15 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>39억</t>
+          <t>42억</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3900000000</v>
+        <v>4200000000</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3948,49 +3948,49 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2631241203</t>
+          <t>2632792587</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>42.8</v>
+        <v>43.8</v>
       </c>
       <c r="F62" t="n">
-        <v>39.7</v>
+        <v>41.2</v>
       </c>
       <c r="G62" t="n">
-        <v>141.57</v>
+        <v>144.85</v>
       </c>
       <c r="H62" t="n">
-        <v>131.08</v>
+        <v>136.34</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>42억</t>
+          <t>41억 5,000</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4200000000</v>
+        <v>4150000000</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2632792587</t>
+          <t>2634165837</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -4022,32 +4022,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>41억 5,000</t>
+          <t>40억</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>4150000000</v>
+        <v>4000000000</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>5/15</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2634165837</t>
+          <t>2631664005</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>중/15</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2631664005</t>
+          <t>2634170812</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>43.8</v>
+        <v>52.5</v>
       </c>
       <c r="F65" t="n">
-        <v>41.2</v>
+        <v>48.6</v>
       </c>
       <c r="G65" t="n">
-        <v>144.85</v>
+        <v>173.63</v>
       </c>
       <c r="H65" t="n">
-        <v>136.34</v>
+        <v>160.74</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>40억</t>
+          <t>44억</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>4000000000</v>
+        <v>4400000000</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>중/15</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4154,14 +4154,14 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2634170812</t>
+          <t>2633967484</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -4211,14 +4211,14 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2633967484</t>
+          <t>2634099689</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -4307,15 +4307,15 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>44억</t>
+          <t>46억</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>4400000000</v>
+        <v>4600000000</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>고/12</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4325,14 +4325,14 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2634099689</t>
+          <t>2632739974</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -4364,15 +4364,15 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>46억</t>
+          <t>43억 9,000</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>4600000000</v>
+        <v>4390000000</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>고/12</t>
+          <t>저/12</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4382,14 +4382,14 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-26T13:35:37</t>
+          <t>2026-06-28T12:09:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2632739974</t>
+          <t>2633201694</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -4421,15 +4421,15 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>43억 9,000</t>
+          <t>45억</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>4390000000</v>
+        <v>4500000000</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>저/12</t>
+          <t>2/12</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -4461,40 +4461,2035 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>2634143650</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>26</v>
+      </c>
+      <c r="F71" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="H71" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30억 5,000</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>3050000000</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2633978112</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H72" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>29억 7,000</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>2970000000</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2634142469</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H73" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>30억</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2631663732</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H74" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>30억</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2632586407</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H75" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>29억 9,500</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>2995000000</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2630437810</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H76" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>31억</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2630439804</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="H77" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>31억</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2634171154</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G78" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="H78" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30억 5,000</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>3050000000</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2632660872</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F79" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="H79" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>29억 7,000</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>2970000000</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2633753342</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G80" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>30억 8,000</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>3080000000</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2633492822</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G81" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="H81" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>30억</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2634439099</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>35억</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2634344796</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F83" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H83" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>34억</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2633805075</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H84" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>34억</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2631662478</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G85" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H85" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>34억 5,000</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>3450000000</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2631661706</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F86" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>35억</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2631661405</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H87" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>34억</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2630690375</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F88" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H88" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>35억</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2634450467</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F89" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G89" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H89" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>41억</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>4100000000</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2634099789</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F90" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G90" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H90" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2633965856</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F91" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G91" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H91" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>39억</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2633977832</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F92" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G92" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H92" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2633130337</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F93" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G93" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H93" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2633978876</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F94" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G94" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H94" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>중/12</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2632656877</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F95" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G95" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H95" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2632708399</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F96" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G96" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H96" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>39억</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2631241203</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F97" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G97" t="n">
+        <v>141.57</v>
+      </c>
+      <c r="H97" t="n">
+        <v>131.08</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>42억</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2632792587</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F98" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="H98" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>41억 5,000</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>4150000000</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2634165837</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F99" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G99" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="H99" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2631664005</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="F100" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="H100" t="n">
+        <v>136.34</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>40억</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>중/15</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2634170812</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F101" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G101" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H101" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>44억</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>4400000000</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2633977168</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G102" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H102" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>46억</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>4600000000</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2633967484</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H103" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>44억</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>4400000000</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2634099689</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G104" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H104" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>46억</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>4600000000</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>고/12</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2632739974</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G105" t="n">
+        <v>173.63</v>
+      </c>
+      <c r="H105" t="n">
+        <v>160.74</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>43억 9,000</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>4390000000</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>저/12</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-26T13:35:37</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>우성1,2,3차</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>2633201694</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E106" t="n">
         <v>52.5</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F106" t="n">
         <v>48.6</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G106" t="n">
         <v>173.63</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H106" t="n">
         <v>160.74</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>45억</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J106" t="n">
         <v>4500000000</v>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2/12</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
